--- a/luban-excels/bak/xlsx/__enums__.xlsx
+++ b/luban-excels/bak/xlsx/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="329">
   <si>
     <t>##var</t>
   </si>
@@ -635,7 +635,7 @@
     <t>活动产出</t>
   </si>
   <si>
-    <t>活动/LinkTree等</t>
+    <t>活动、渠道或限时玩法使用的奖励盲盒。</t>
   </si>
   <si>
     <t>Retired</t>
@@ -990,6 +990,30 @@
   </si>
   <si>
     <t>正式版</t>
+  </si>
+  <si>
+    <t>ERewardSelectionMode</t>
+  </si>
+  <si>
+    <t>奖励选择模式</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>按照 BlindBoxItemWeight 配置的权重抽取，允许重复获得此前抽中的物品。</t>
+  </si>
+  <si>
+    <t>ExcludeDrawnInThisBox</t>
+  </si>
+  <si>
+    <t>排除该盲盒中曾抽中的</t>
+  </si>
+  <si>
+    <t>抽取时排除玩家此前从同一个盲盒中抽中的物品；其他盲盒抽中的同一道具不计入排除范围。（客户端盲盒专用，状态是否跨设备取决于云存档的最终设计）</t>
   </si>
 </sst>
 </file>
@@ -1979,7 +2003,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L125"/>
+  <dimension ref="A1:L127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="1" customWidth="1"/>
@@ -4168,6 +4192,46 @@
         <v>8</v>
       </c>
     </row>
+    <row r="126" spans="2:12">
+      <c r="B126" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C126" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D126" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="J126" s="1">
+        <v>1</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="127" spans="2:12">
+      <c r="H127" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="J127" s="1">
+        <v>2</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
